--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108684531</v>
+        <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>57825</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100096</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,28 +708,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hygge NV St Ötjärnen, Stora Ötjärn, Lindome, Hl</t>
+          <t>Brännås, Lindome, Brännås, Lindome, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334510</v>
+        <v>334367</v>
       </c>
       <c r="R2" t="n">
-        <v>6386203</v>
+        <v>6386712</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bo byggdes av par 2022. Föryngring okänd. En fågel återvänt 1/5</t>
+          <t>Spillkråkehack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +794,363 @@
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136920358</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136921240</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brännås, Lindome, Brännås, Lindome, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>334357</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6386645</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spillkråkehack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mats Foss, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921240</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136921750</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>N St Ötjärnen, N St Ötjärnen, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>334340</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6386510</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillkråkehack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mats Foss, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136921750</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108684531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57825</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100096</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pandion haliaetus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hygge NV St Ötjärnen, Stora Ötjärn, Lindome, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334510</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6386203</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bo byggdes av par 2022. Föryngring okänd. En fågel återvänt 1/5</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Foss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/108684531</t>
         </is>
@@ -796,6 +1159,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136921240</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136921750</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136921240</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136921750</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136921240</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136921750</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136921240</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136921750</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136921240</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136921750</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46379-2025 artfynd.xlsx
+++ b/artfynd/A 46379-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136920358</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136921240</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136921750</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
